--- a/test_cli/leveling_test/Templete_2025_0828.xlsx
+++ b/test_cli/leveling_test/Templete_2025_0828.xlsx
@@ -1,15 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView windowWidth="28800" windowHeight="13160"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sumarry" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Z Stage" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="8CH Pipette" sheetId="3" r:id="rId7"/>
-    <sheet state="visible" name="96CH Pipette" sheetId="4" r:id="rId8"/>
+    <sheet name="Sumarry" sheetId="1" r:id="rId1"/>
+    <sheet name="Z Stage" sheetId="2" r:id="rId2"/>
+    <sheet name="8CH Pipette" sheetId="3" r:id="rId3"/>
+    <sheet name="96CH Pipette" sheetId="4" r:id="rId4"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -352,56 +368,230 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="29">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF4285F4"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
-    </font>
-    <font/>
-    <font>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <color rgb="FF4285F4"/>
-      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -421,9 +611,201 @@
         <bgColor rgb="FF4A86E8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="17">
-    <border/>
+  <borders count="25">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thick">
         <color rgb="FF000000"/>
@@ -437,6 +819,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -451,6 +834,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -465,6 +849,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
@@ -479,6 +864,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -493,19 +879,34 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -515,8 +916,10 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thick">
         <color rgb="FF000000"/>
       </right>
@@ -526,6 +929,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
@@ -537,6 +941,8 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -551,6 +957,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
@@ -559,9 +966,9 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
@@ -570,6 +977,11 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
@@ -578,9 +990,11 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -595,6 +1009,7 @@
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -609,150 +1024,592 @@
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="17" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="9" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+  <cellXfs count="36">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="10" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="11" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="10" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="12" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="13" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="14" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="14" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="14" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="15" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="16" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="10" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="14" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="14" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="15" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -942,894 +1799,859 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:I27"/>
+  <sheetFormatPr defaultColWidth="12.6339285714286" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="26.13"/>
-    <col customWidth="1" min="2" max="2" width="9.25"/>
-    <col customWidth="1" min="3" max="3" width="31.63"/>
-    <col customWidth="1" min="4" max="4" width="8.0"/>
-    <col customWidth="1" min="5" max="5" width="15.63"/>
-    <col customWidth="1" min="6" max="6" width="9.0"/>
-    <col customWidth="1" min="7" max="7" width="17.75"/>
-    <col customWidth="1" min="8" max="8" width="9.75"/>
+    <col min="1" max="1" width="26.1339285714286" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="31.6339285714286" customWidth="1"/>
+    <col min="4" max="4" width="8" customWidth="1"/>
+    <col min="5" max="5" width="15.6339285714286" customWidth="1"/>
+    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="7" max="7" width="17.75" customWidth="1"/>
+    <col min="8" max="8" width="9.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2">
+    <row r="1" customHeight="1" spans="1:4">
+      <c r="A1" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="33">
         <f>'Z Stage'!F5</f>
-        <v>0.014</v>
-      </c>
-      <c r="C1" s="1" t="s">
+        <v>0.0139999999999993</v>
+      </c>
+      <c r="C1" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2">
+      <c r="D1" s="33">
         <f>'Z Stage'!G5</f>
         <v>0</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="1" t="s">
+    <row r="2" customHeight="1" spans="1:4">
+      <c r="A2" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="33">
         <f>'Z Stage'!F7</f>
-        <v>-0.056</v>
-      </c>
-      <c r="C2" s="1" t="s">
+        <v>-0.0560000000000009</v>
+      </c>
+      <c r="C2" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="33">
         <f>'Z Stage'!G7</f>
         <v>0</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="s">
+    <row r="3" customHeight="1" spans="1:4">
+      <c r="A3" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="33">
         <f>'Z Stage'!F8</f>
-        <v>-0.07</v>
-      </c>
-      <c r="C3" s="1" t="s">
+        <v>-0.0700000000000003</v>
+      </c>
+      <c r="C3" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="33">
         <f>'Z Stage'!G8</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="s">
+    <row r="4" customHeight="1" spans="1:4">
+      <c r="A4" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="33">
         <f>'Z Stage'!F9</f>
-        <v>-0.062</v>
-      </c>
-      <c r="C4" s="1" t="s">
+        <v>-0.0620000000000012</v>
+      </c>
+      <c r="C4" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="33">
         <f>'Z Stage'!G9</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="s">
+    <row r="5" customHeight="1" spans="1:4">
+      <c r="A5" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="33">
         <f>'Z Stage'!F10</f>
-        <v>-0.17</v>
-      </c>
-      <c r="C5" s="1" t="s">
+        <v>-0.169999999999998</v>
+      </c>
+      <c r="C5" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="33">
         <f>'Z Stage'!G10</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="s">
+    <row r="6" customHeight="1" spans="1:4">
+      <c r="A6" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="33">
         <f>'Z Stage'!F11</f>
-        <v>-0.088</v>
-      </c>
-      <c r="C6" s="1" t="s">
+        <v>-0.0879999999999974</v>
+      </c>
+      <c r="C6" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="33">
         <f>'Z Stage'!G11</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="s">
+    <row r="7" customHeight="1" spans="1:4">
+      <c r="A7" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="33">
         <f>'Z Stage'!F12</f>
-        <v>-0.068</v>
-      </c>
-      <c r="C7" s="1" t="s">
+        <v>-0.0679999999999978</v>
+      </c>
+      <c r="C7" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="33">
         <f>'Z Stage'!G12</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="s">
+    <row r="8" customHeight="1" spans="1:4">
+      <c r="A8" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="33">
         <f>'Z Stage'!F13</f>
-        <v>-0.098</v>
-      </c>
-      <c r="C8" s="1" t="s">
+        <v>-0.097999999999999</v>
+      </c>
+      <c r="C8" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="33">
         <f>'Z Stage'!G13</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="s">
+    <row r="9" customHeight="1" spans="1:4">
+      <c r="A9" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="33">
         <f>'Z Stage'!F14</f>
-        <v>-0.03</v>
-      </c>
-      <c r="C9" s="1" t="s">
+        <v>-0.0300000000000011</v>
+      </c>
+      <c r="C9" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="33">
         <f>'Z Stage'!G14</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="s">
+    <row r="10" customHeight="1" spans="1:4">
+      <c r="A10" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="33">
         <f>'Z Stage'!F15</f>
-        <v>-0.044</v>
-      </c>
-      <c r="C10" s="1" t="s">
+        <v>-0.0439999999999969</v>
+      </c>
+      <c r="C10" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="33">
         <f>'Z Stage'!G15</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="s">
+    <row r="11" customHeight="1" spans="1:4">
+      <c r="A11" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="33">
         <f>'Z Stage'!F16</f>
-        <v>-0.05</v>
-      </c>
-      <c r="C11" s="1" t="s">
+        <v>-0.0499999999999972</v>
+      </c>
+      <c r="C11" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="33">
         <f>'Z Stage'!G16</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="s">
+    <row r="12" customHeight="1" spans="1:4">
+      <c r="A12" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="33">
         <f>'Z Stage'!F17</f>
-        <v>-0.15</v>
-      </c>
-      <c r="C12" s="1" t="s">
+        <v>-0.150000000000002</v>
+      </c>
+      <c r="C12" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="33">
         <f>'Z Stage'!G17</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="s">
+    <row r="13" customHeight="1" spans="1:4">
+      <c r="A13" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="33">
         <f>'Z Stage'!F18</f>
-        <v>-0.058</v>
-      </c>
-      <c r="C13" s="1" t="s">
+        <v>-0.0579999999999998</v>
+      </c>
+      <c r="C13" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="33">
         <f>'Z Stage'!G18</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
+    <row r="14" customHeight="1" spans="1:4">
+      <c r="A14" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="33">
         <f>'8CH Pipette'!F5</f>
-        <v>0.024</v>
-      </c>
-      <c r="C14" s="3" t="s">
+        <v>0.0240000000000009</v>
+      </c>
+      <c r="C14" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="33">
         <f>'8CH Pipette'!G5</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
+    <row r="15" customHeight="1" spans="1:4">
+      <c r="A15" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="33">
         <f>'8CH Pipette'!F7</f>
-        <v>0.06</v>
-      </c>
-      <c r="C15" s="3" t="s">
+        <v>0.0599999999999987</v>
+      </c>
+      <c r="C15" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="33">
         <f>'8CH Pipette'!G7</f>
         <v>0</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
+    <row r="16" customHeight="1" spans="1:4">
+      <c r="A16" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="33">
         <f>'8CH Pipette'!F8</f>
         <v>0.032</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="33">
         <f>'8CH Pipette'!G8</f>
         <v>0</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="3" t="s">
+    <row r="17" customHeight="1" spans="1:9">
+      <c r="A17" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="33">
         <f>'8CH Pipette'!F9</f>
         <v>0.032</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="33">
         <f>'8CH Pipette'!G9</f>
         <v>0</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="s">
+    <row r="18" customHeight="1" spans="1:9">
+      <c r="A18" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="33">
         <f>'96CH Pipette'!H5</f>
-        <v>-0.006</v>
-      </c>
-      <c r="C18" s="4" t="s">
+        <v>-0.00600000000000023</v>
+      </c>
+      <c r="C18" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="33">
         <f>'96CH Pipette'!I5</f>
         <v>0</v>
       </c>
-      <c r="F18" s="2" t="str">
-        <f>'96CH Pipette'!J5</f>
-        <v/>
-      </c>
-      <c r="H18" s="2" t="str">
-        <f>'96CH Pipette'!K5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="s">
+      <c r="F18" s="33"/>
+      <c r="H18" s="33"/>
+    </row>
+    <row r="19" customHeight="1" spans="1:9">
+      <c r="A19" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="33">
         <f>'96CH Pipette'!H7</f>
-        <v>-0.054</v>
-      </c>
-      <c r="C19" s="4" t="s">
+        <v>-0.054000000000002</v>
+      </c>
+      <c r="C19" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="33">
         <f>'96CH Pipette'!I7</f>
         <v>0</v>
       </c>
-      <c r="F19" s="2" t="str">
-        <f>'96CH Pipette'!J7</f>
-        <v/>
-      </c>
-      <c r="H19" s="2" t="str">
-        <f>'96CH Pipette'!K7</f>
-        <v/>
-      </c>
-      <c r="I19" s="2" t="str">
-        <f>'96CH Pipette'!L7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="s">
+      <c r="F19" s="33"/>
+      <c r="H19" s="33"/>
+      <c r="I19" s="33"/>
+    </row>
+    <row r="20" customHeight="1" spans="1:9">
+      <c r="A20" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20" s="33">
         <f>'96CH Pipette'!H9</f>
-        <v>-0.086</v>
-      </c>
-      <c r="C20" s="4" t="s">
+        <v>-0.0860000000000021</v>
+      </c>
+      <c r="C20" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20" s="33">
         <f>'96CH Pipette'!I9</f>
         <v>0</v>
       </c>
-      <c r="F20" s="2" t="str">
-        <f>'96CH Pipette'!J9</f>
-        <v/>
-      </c>
-      <c r="H20" s="2" t="str">
-        <f>'96CH Pipette'!K9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="s">
+      <c r="F20" s="33"/>
+      <c r="H20" s="33"/>
+    </row>
+    <row r="21" customHeight="1" spans="1:9">
+      <c r="A21" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="33">
         <f>'96CH Pipette'!H11</f>
         <v>0</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="33">
         <f>'96CH Pipette'!I11</f>
-        <v>0.054</v>
-      </c>
-      <c r="F21" s="2" t="str">
-        <f>'96CH Pipette'!J11</f>
-        <v/>
-      </c>
-      <c r="H21" s="2" t="str">
-        <f>'96CH Pipette'!K11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="s">
+        <v>0.054000000000002</v>
+      </c>
+      <c r="F21" s="33"/>
+      <c r="H21" s="33"/>
+    </row>
+    <row r="22" customHeight="1" spans="1:9">
+      <c r="A22" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" s="33">
         <f>'96CH Pipette'!H12</f>
         <v>0</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" s="33">
         <f>'96CH Pipette'!I12</f>
-        <v>0.036</v>
-      </c>
-      <c r="F22" s="2" t="str">
-        <f>'96CH Pipette'!J12</f>
-        <v/>
-      </c>
-      <c r="H22" s="2" t="str">
-        <f>'96CH Pipette'!K12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="s">
+        <v>0.0360000000000014</v>
+      </c>
+      <c r="F22" s="33"/>
+      <c r="H22" s="33"/>
+    </row>
+    <row r="23" customHeight="1" spans="1:9">
+      <c r="A23" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23" s="33">
         <f>'96CH Pipette'!H13</f>
         <v>0</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="33">
         <f>'96CH Pipette'!I13</f>
-        <v>0.048</v>
-      </c>
-      <c r="F23" s="2" t="str">
-        <f>'96CH Pipette'!J13</f>
-        <v/>
-      </c>
-      <c r="H23" s="2" t="str">
-        <f>'96CH Pipette'!K13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="s">
+        <v>0.0480000000000018</v>
+      </c>
+      <c r="F23" s="33"/>
+      <c r="H23" s="33"/>
+    </row>
+    <row r="24" customHeight="1" spans="1:9">
+      <c r="A24" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B24" s="33">
         <f>'96CH Pipette'!H15</f>
-        <v>-0.056</v>
-      </c>
-      <c r="C24" s="4" t="s">
+        <v>-0.0559999999999974</v>
+      </c>
+      <c r="C24" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24" s="33">
         <f>'96CH Pipette'!I15</f>
-        <v>-0.078</v>
-      </c>
-      <c r="E24" s="4" t="s">
+        <v>-0.0779999999999994</v>
+      </c>
+      <c r="E24" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F24" s="33">
         <f>'96CH Pipette'!J15</f>
         <v>0</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G24" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="H24" s="2">
+      <c r="H24" s="33">
         <f>'96CH Pipette'!K15</f>
-        <v>0.082</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="s">
+        <v>0.0820000000000007</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="1:9">
+      <c r="A25" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B25" s="33">
         <f>'96CH Pipette'!H16</f>
-        <v>-0.058</v>
-      </c>
-      <c r="C25" s="4" t="s">
+        <v>-0.0580000000000034</v>
+      </c>
+      <c r="C25" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="33">
         <f>'96CH Pipette'!I16</f>
-        <v>-0.092</v>
-      </c>
-      <c r="E25" s="4" t="s">
+        <v>-0.0920000000000023</v>
+      </c>
+      <c r="E25" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F25" s="33">
         <f>'96CH Pipette'!J16</f>
         <v>0</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="G25" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="H25" s="2">
+      <c r="H25" s="33">
         <f>'96CH Pipette'!K16</f>
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="s">
+        <v>0.0499999999999972</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="1:9">
+      <c r="A26" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B26" s="33">
         <f>'96CH Pipette'!H17</f>
-        <v>0.062</v>
-      </c>
-      <c r="C26" s="4" t="s">
+        <v>0.0620000000000012</v>
+      </c>
+      <c r="C26" s="35" t="s">
         <v>55</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26" s="33">
         <f>'96CH Pipette'!I17</f>
-        <v>0.14</v>
-      </c>
-      <c r="E26" s="4" t="s">
+        <v>0.140000000000001</v>
+      </c>
+      <c r="E26" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F26" s="33">
         <f>'96CH Pipette'!J17</f>
         <v>0</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G26" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="H26" s="2">
+      <c r="H26" s="33">
         <f>'96CH Pipette'!K17</f>
-        <v>0.016</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="s">
+        <v>0.0159999999999982</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="1:9">
+      <c r="A27" s="35" t="s">
         <v>58</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B27" s="33">
         <f>'96CH Pipette'!H18</f>
-        <v>-0.056</v>
-      </c>
-      <c r="C27" s="4" t="s">
+        <v>-0.0560000000000009</v>
+      </c>
+      <c r="C27" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D27" s="33">
         <f>'96CH Pipette'!I18</f>
-        <v>-0.09</v>
-      </c>
-      <c r="E27" s="4" t="s">
+        <v>-0.0899999999999999</v>
+      </c>
+      <c r="E27" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="F27" s="2">
+      <c r="F27" s="33">
         <f>'96CH Pipette'!J18</f>
         <v>0</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="G27" s="35" t="s">
         <v>61</v>
       </c>
-      <c r="H27" s="2">
+      <c r="H27" s="33">
         <f>'96CH Pipette'!K18</f>
-        <v>0.078</v>
+        <v>0.0779999999999994</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="B2:G18"/>
+  <sheetFormatPr defaultColWidth="12.6339285714286" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="6"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="3.13"/>
+    <col min="1" max="1" width="3.13392857142857" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="B2" s="5" t="s">
+    <row r="2" customHeight="1" spans="2:7">
+      <c r="B2" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="7"/>
-    </row>
-    <row r="3">
-      <c r="B3" s="8" t="s">
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="3"/>
+    </row>
+    <row r="3" customHeight="1" spans="2:7">
+      <c r="B3" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C3" s="9">
-        <v>45897.0</v>
-      </c>
-      <c r="D3" s="10" t="s">
+      <c r="C3" s="5">
+        <v>45897</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E3" s="11"/>
-      <c r="F3" s="10" t="s">
+      <c r="E3" s="8"/>
+      <c r="F3" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="G3" s="12"/>
-    </row>
-    <row r="4">
-      <c r="B4" s="13" t="s">
+      <c r="G3" s="9"/>
+    </row>
+    <row r="4" customHeight="1" spans="2:7">
+      <c r="B4" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="G4" s="15" t="s">
+      <c r="G4" s="21" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="16"/>
-      <c r="C5" s="17" t="s">
+    <row r="5" customHeight="1" spans="2:7">
+      <c r="B5" s="20"/>
+      <c r="C5" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="12">
         <v>30.024</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="12">
         <v>30.038</v>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="28">
         <f>E5-D5</f>
-        <v>0.014</v>
-      </c>
-      <c r="G5" s="19">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="13" t="s">
+        <v>0.0139999999999993</v>
+      </c>
+      <c r="G5" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="2:7">
+      <c r="B6" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="G6" s="15" t="s">
+      <c r="G6" s="21" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="20"/>
-      <c r="C7" s="21" t="s">
+    <row r="7" customHeight="1" spans="2:7">
+      <c r="B7" s="14"/>
+      <c r="C7" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="12">
         <v>30.346</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="12">
         <v>30.29</v>
       </c>
-      <c r="F7" s="18">
-        <f t="shared" ref="F7:F18" si="1">E7-D7</f>
-        <v>-0.056</v>
-      </c>
-      <c r="G7" s="19">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="20"/>
-      <c r="C8" s="21" t="s">
+      <c r="F7" s="28">
+        <f t="shared" ref="F7:F18" si="0">E7-D7</f>
+        <v>-0.0560000000000009</v>
+      </c>
+      <c r="G7" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="2:7">
+      <c r="B8" s="14"/>
+      <c r="C8" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="12">
         <v>29.944</v>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="12">
         <v>29.874</v>
       </c>
-      <c r="F8" s="18">
-        <f t="shared" si="1"/>
-        <v>-0.07</v>
-      </c>
-      <c r="G8" s="19">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="20"/>
-      <c r="C9" s="21" t="s">
+      <c r="F8" s="28">
+        <f t="shared" si="0"/>
+        <v>-0.0700000000000003</v>
+      </c>
+      <c r="G8" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="2:7">
+      <c r="B9" s="14"/>
+      <c r="C9" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="12">
         <v>30.122</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="12">
         <v>30.06</v>
       </c>
-      <c r="F9" s="18">
-        <f t="shared" si="1"/>
-        <v>-0.062</v>
-      </c>
-      <c r="G9" s="19">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="20"/>
-      <c r="C10" s="21" t="s">
+      <c r="F9" s="28">
+        <f t="shared" si="0"/>
+        <v>-0.0620000000000012</v>
+      </c>
+      <c r="G9" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="2:7">
+      <c r="B10" s="14"/>
+      <c r="C10" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="12">
         <v>30.048</v>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="12">
         <v>29.878</v>
       </c>
-      <c r="F10" s="18">
-        <f t="shared" si="1"/>
-        <v>-0.17</v>
-      </c>
-      <c r="G10" s="19">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="20"/>
-      <c r="C11" s="21" t="s">
+      <c r="F10" s="28">
+        <f t="shared" si="0"/>
+        <v>-0.169999999999998</v>
+      </c>
+      <c r="G10" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="2:7">
+      <c r="B11" s="14"/>
+      <c r="C11" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="12">
         <v>29.894</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="12">
         <v>29.806</v>
       </c>
-      <c r="F11" s="18">
-        <f t="shared" si="1"/>
-        <v>-0.088</v>
-      </c>
-      <c r="G11" s="19">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="20"/>
-      <c r="C12" s="21" t="s">
+      <c r="F11" s="28">
+        <f t="shared" si="0"/>
+        <v>-0.0879999999999974</v>
+      </c>
+      <c r="G11" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="2:7">
+      <c r="B12" s="14"/>
+      <c r="C12" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="12">
         <v>30.04</v>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="12">
         <v>29.972</v>
       </c>
-      <c r="F12" s="18">
-        <f t="shared" si="1"/>
-        <v>-0.068</v>
-      </c>
-      <c r="G12" s="19">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="20"/>
-      <c r="C13" s="21" t="s">
+      <c r="F12" s="28">
+        <f t="shared" si="0"/>
+        <v>-0.0679999999999978</v>
+      </c>
+      <c r="G12" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="2:7">
+      <c r="B13" s="14"/>
+      <c r="C13" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="D13" s="17">
+      <c r="D13" s="12">
         <v>30.124</v>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="12">
         <v>30.026</v>
       </c>
-      <c r="F13" s="18">
-        <f t="shared" si="1"/>
-        <v>-0.098</v>
-      </c>
-      <c r="G13" s="19">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="20"/>
-      <c r="C14" s="21" t="s">
+      <c r="F13" s="28">
+        <f t="shared" si="0"/>
+        <v>-0.097999999999999</v>
+      </c>
+      <c r="G13" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="2:7">
+      <c r="B14" s="14"/>
+      <c r="C14" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="D14" s="17">
+      <c r="D14" s="12">
         <v>30.12</v>
       </c>
-      <c r="E14" s="17">
+      <c r="E14" s="12">
         <v>30.09</v>
       </c>
-      <c r="F14" s="18">
-        <f t="shared" si="1"/>
-        <v>-0.03</v>
-      </c>
-      <c r="G14" s="19">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="20"/>
-      <c r="C15" s="21" t="s">
+      <c r="F14" s="28">
+        <f t="shared" si="0"/>
+        <v>-0.0300000000000011</v>
+      </c>
+      <c r="G14" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="2:7">
+      <c r="B15" s="14"/>
+      <c r="C15" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="12">
         <v>30.15</v>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="12">
         <v>30.106</v>
       </c>
-      <c r="F15" s="18">
-        <f t="shared" si="1"/>
-        <v>-0.044</v>
-      </c>
-      <c r="G15" s="19">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="20"/>
-      <c r="C16" s="21" t="s">
+      <c r="F15" s="28">
+        <f t="shared" si="0"/>
+        <v>-0.0439999999999969</v>
+      </c>
+      <c r="G15" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="2:7">
+      <c r="B16" s="14"/>
+      <c r="C16" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="D16" s="17">
+      <c r="D16" s="12">
         <v>30.086</v>
       </c>
-      <c r="E16" s="17">
+      <c r="E16" s="12">
         <v>30.036</v>
       </c>
-      <c r="F16" s="18">
-        <f t="shared" si="1"/>
-        <v>-0.05</v>
-      </c>
-      <c r="G16" s="19">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="20"/>
-      <c r="C17" s="21" t="s">
+      <c r="F16" s="28">
+        <f t="shared" si="0"/>
+        <v>-0.0499999999999972</v>
+      </c>
+      <c r="G16" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="2:7">
+      <c r="B17" s="14"/>
+      <c r="C17" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="D17" s="17">
+      <c r="D17" s="12">
         <v>30.036</v>
       </c>
-      <c r="E17" s="17">
+      <c r="E17" s="12">
         <v>29.886</v>
       </c>
-      <c r="F17" s="18">
-        <f t="shared" si="1"/>
-        <v>-0.15</v>
-      </c>
-      <c r="G17" s="19">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="22"/>
-      <c r="C18" s="23" t="s">
+      <c r="F17" s="28">
+        <f t="shared" si="0"/>
+        <v>-0.150000000000002</v>
+      </c>
+      <c r="G17" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="2:7">
+      <c r="B18" s="23"/>
+      <c r="C18" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="D18" s="24">
+      <c r="D18" s="29">
         <v>30.08</v>
       </c>
-      <c r="E18" s="24">
+      <c r="E18" s="29">
         <v>30.022</v>
       </c>
-      <c r="F18" s="25">
-        <f t="shared" si="1"/>
-        <v>-0.058</v>
-      </c>
-      <c r="G18" s="26">
-        <v>0.0</v>
+      <c r="F18" s="30">
+        <f t="shared" si="0"/>
+        <v>-0.0579999999999998</v>
+      </c>
+      <c r="G18" s="31">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1839,162 +2661,164 @@
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="B6:B18"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="B2:G9"/>
+  <sheetFormatPr defaultColWidth="12.6339285714286" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="6"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="3.38"/>
+    <col min="1" max="1" width="3.38392857142857" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="B2" s="5" t="s">
+    <row r="2" customHeight="1" spans="2:7">
+      <c r="B2" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="7"/>
-    </row>
-    <row r="3">
-      <c r="B3" s="8" t="s">
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="3"/>
+    </row>
+    <row r="3" customHeight="1" spans="2:7">
+      <c r="B3" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C3" s="9">
-        <v>45897.0</v>
-      </c>
-      <c r="D3" s="10" t="s">
+      <c r="C3" s="5">
+        <v>45897</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E3" s="11"/>
-      <c r="F3" s="10" t="s">
+      <c r="E3" s="8"/>
+      <c r="F3" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="G3" s="12"/>
-    </row>
-    <row r="4">
-      <c r="B4" s="13" t="s">
+      <c r="G3" s="9"/>
+    </row>
+    <row r="4" customHeight="1" spans="2:7">
+      <c r="B4" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="G4" s="15" t="s">
+      <c r="G4" s="21" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="16"/>
-      <c r="C5" s="17" t="s">
+    <row r="5" customHeight="1" spans="2:7">
+      <c r="B5" s="20"/>
+      <c r="C5" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="12">
         <v>30.034</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="12">
         <v>30.058</v>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="28">
         <f>E5-D5</f>
-        <v>0.024</v>
-      </c>
-      <c r="G5" s="19">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="13" t="s">
+        <v>0.0240000000000009</v>
+      </c>
+      <c r="G5" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="2:7">
+      <c r="B6" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="G6" s="15" t="s">
+      <c r="G6" s="21" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="20"/>
-      <c r="C7" s="17" t="s">
+    <row r="7" customHeight="1" spans="2:7">
+      <c r="B7" s="14"/>
+      <c r="C7" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="12">
         <v>30.026</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="12">
         <v>30.086</v>
       </c>
-      <c r="F7" s="18">
-        <f t="shared" ref="F7:F9" si="1">E7-D7</f>
-        <v>0.06</v>
-      </c>
-      <c r="G7" s="19">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="20"/>
-      <c r="C8" s="17" t="s">
+      <c r="F7" s="28">
+        <f t="shared" ref="F7:F9" si="0">E7-D7</f>
+        <v>0.0599999999999987</v>
+      </c>
+      <c r="G7" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="2:7">
+      <c r="B8" s="14"/>
+      <c r="C8" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="12">
         <v>30.008</v>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="12">
         <v>30.04</v>
       </c>
-      <c r="F8" s="18">
-        <f t="shared" si="1"/>
+      <c r="F8" s="28">
+        <f t="shared" si="0"/>
         <v>0.032</v>
       </c>
-      <c r="G8" s="19">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="22"/>
-      <c r="C9" s="24" t="s">
+      <c r="G8" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="2:7">
+      <c r="B9" s="23"/>
+      <c r="C9" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="29">
         <v>30.02</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="29">
         <v>30.052</v>
       </c>
-      <c r="F9" s="25">
-        <f t="shared" si="1"/>
+      <c r="F9" s="30">
+        <f t="shared" si="0"/>
         <v>0.032</v>
       </c>
-      <c r="G9" s="26">
-        <v>0.0</v>
+      <c r="G9" s="31">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2004,448 +2828,450 @@
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="B6:B9"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="B2:K18"/>
+  <sheetFormatPr defaultColWidth="12.6339285714286" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="3.38"/>
+    <col min="1" max="1" width="3.38392857142857" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="B2" s="27" t="s">
+    <row r="2" customHeight="1" spans="2:11">
+      <c r="B2" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="7"/>
-    </row>
-    <row r="3">
-      <c r="B3" s="28" t="s">
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="3"/>
+    </row>
+    <row r="3" customHeight="1" spans="2:11">
+      <c r="B3" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C3" s="9">
-        <v>45897.0</v>
-      </c>
-      <c r="D3" s="10" t="s">
+      <c r="C3" s="5">
+        <v>45897</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="10" t="s">
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
-      <c r="K3" s="12"/>
-    </row>
-    <row r="4">
-      <c r="B4" s="13" t="s">
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="9"/>
+    </row>
+    <row r="4" customHeight="1" spans="2:11">
+      <c r="B4" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="14" t="s">
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="I4" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="J4" s="17"/>
-      <c r="K4" s="19"/>
-    </row>
-    <row r="5">
-      <c r="B5" s="20"/>
-      <c r="C5" s="21" t="s">
+      <c r="J4" s="12"/>
+      <c r="K4" s="13"/>
+    </row>
+    <row r="5" customHeight="1" spans="2:11">
+      <c r="B5" s="14"/>
+      <c r="C5" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="16">
         <v>29.974</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="16">
         <v>29.968</v>
       </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="31">
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="17">
         <f>E5-D5</f>
-        <v>-0.006</v>
-      </c>
-      <c r="I5" s="31">
-        <v>0.0</v>
-      </c>
-      <c r="J5" s="17"/>
-      <c r="K5" s="19"/>
-    </row>
-    <row r="6">
-      <c r="B6" s="20"/>
-      <c r="C6" s="14" t="s">
+        <v>-0.00600000000000023</v>
+      </c>
+      <c r="I5" s="17">
+        <v>0</v>
+      </c>
+      <c r="J5" s="12"/>
+      <c r="K5" s="13"/>
+    </row>
+    <row r="6" customHeight="1" spans="2:11">
+      <c r="B6" s="14"/>
+      <c r="C6" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="14" t="s">
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="I6" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="J6" s="17"/>
-      <c r="K6" s="19"/>
-    </row>
-    <row r="7">
-      <c r="B7" s="20"/>
-      <c r="C7" s="21" t="s">
+      <c r="J6" s="12"/>
+      <c r="K6" s="13"/>
+    </row>
+    <row r="7" customHeight="1" spans="2:11">
+      <c r="B7" s="14"/>
+      <c r="C7" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="16">
         <v>30.082</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="16">
         <v>30.028</v>
       </c>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="32">
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="18">
         <f>E7-D7</f>
-        <v>-0.054</v>
-      </c>
-      <c r="I7" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="J7" s="17"/>
-      <c r="K7" s="19"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="20"/>
-      <c r="C8" s="14" t="s">
+        <v>-0.054000000000002</v>
+      </c>
+      <c r="I7" s="19">
+        <v>0</v>
+      </c>
+      <c r="J7" s="12"/>
+      <c r="K7" s="13"/>
+    </row>
+    <row r="8" customHeight="1" spans="2:11">
+      <c r="B8" s="14"/>
+      <c r="C8" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="14" t="s">
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="I8" s="14" t="s">
+      <c r="I8" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="J8" s="17"/>
-      <c r="K8" s="19"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="16"/>
-      <c r="C9" s="21" t="s">
+      <c r="J8" s="12"/>
+      <c r="K8" s="13"/>
+    </row>
+    <row r="9" customHeight="1" spans="2:11">
+      <c r="B9" s="20"/>
+      <c r="C9" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="16">
         <v>30.088</v>
       </c>
-      <c r="E9" s="33">
+      <c r="E9" s="19">
         <v>30.002</v>
       </c>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="31">
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="17">
         <f>E9-D9</f>
-        <v>-0.086</v>
-      </c>
-      <c r="I9" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="J9" s="17"/>
-      <c r="K9" s="19"/>
-    </row>
-    <row r="10">
-      <c r="B10" s="13" t="s">
+        <v>-0.0860000000000021</v>
+      </c>
+      <c r="I9" s="19">
+        <v>0</v>
+      </c>
+      <c r="J9" s="12"/>
+      <c r="K9" s="13"/>
+    </row>
+    <row r="10" customHeight="1" spans="2:11">
+      <c r="B10" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="14" t="s">
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="I10" s="14" t="s">
+      <c r="I10" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="J10" s="17"/>
-      <c r="K10" s="19"/>
-    </row>
-    <row r="11">
-      <c r="B11" s="20"/>
-      <c r="C11" s="21" t="s">
+      <c r="J10" s="12"/>
+      <c r="K10" s="13"/>
+    </row>
+    <row r="11" customHeight="1" spans="2:11">
+      <c r="B11" s="14"/>
+      <c r="C11" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="16">
         <v>30.056</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="16">
         <v>30.002</v>
       </c>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="I11" s="31">
-        <f t="shared" ref="I11:I13" si="1">D11-E11</f>
-        <v>0.054</v>
-      </c>
-      <c r="J11" s="17"/>
-      <c r="K11" s="19"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="20"/>
-      <c r="C12" s="21" t="s">
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="19">
+        <v>0</v>
+      </c>
+      <c r="I11" s="17">
+        <f t="shared" ref="I11:I13" si="0">D11-E11</f>
+        <v>0.054000000000002</v>
+      </c>
+      <c r="J11" s="12"/>
+      <c r="K11" s="13"/>
+    </row>
+    <row r="12" customHeight="1" spans="2:11">
+      <c r="B12" s="14"/>
+      <c r="C12" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="16">
         <v>29.966</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="16">
         <v>29.93</v>
       </c>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="I12" s="31">
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="19">
+        <v>0</v>
+      </c>
+      <c r="I12" s="17">
+        <f t="shared" si="0"/>
+        <v>0.0360000000000014</v>
+      </c>
+      <c r="J12" s="12"/>
+      <c r="K12" s="13"/>
+    </row>
+    <row r="13" customHeight="1" spans="2:11">
+      <c r="B13" s="20"/>
+      <c r="C13" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="D13" s="16">
+        <v>30.064</v>
+      </c>
+      <c r="E13" s="16">
+        <v>30.016</v>
+      </c>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="19">
+        <v>0</v>
+      </c>
+      <c r="I13" s="17">
+        <f t="shared" si="0"/>
+        <v>0.0480000000000018</v>
+      </c>
+      <c r="J13" s="12"/>
+      <c r="K13" s="13"/>
+    </row>
+    <row r="14" customHeight="1" spans="2:11">
+      <c r="B14" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="K14" s="21" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="2:11">
+      <c r="B15" s="14"/>
+      <c r="C15" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="D15" s="16">
+        <v>30.15</v>
+      </c>
+      <c r="E15" s="16">
+        <v>30.172</v>
+      </c>
+      <c r="F15" s="16">
+        <v>30.094</v>
+      </c>
+      <c r="G15" s="16">
+        <v>30.012</v>
+      </c>
+      <c r="H15" s="17">
+        <f t="shared" ref="H15:H18" si="1">F15-D15</f>
+        <v>-0.0559999999999974</v>
+      </c>
+      <c r="I15" s="17">
+        <f t="shared" ref="I15:I18" si="2">F15-E15</f>
+        <v>-0.0779999999999994</v>
+      </c>
+      <c r="J15" s="17">
+        <v>0</v>
+      </c>
+      <c r="K15" s="22">
+        <f t="shared" ref="K15:K18" si="3">F15-G15</f>
+        <v>0.0820000000000007</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="2:11">
+      <c r="B16" s="14"/>
+      <c r="C16" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="D16" s="16">
+        <v>30.138</v>
+      </c>
+      <c r="E16" s="16">
+        <v>30.172</v>
+      </c>
+      <c r="F16" s="16">
+        <v>30.08</v>
+      </c>
+      <c r="G16" s="16">
+        <v>30.03</v>
+      </c>
+      <c r="H16" s="17">
         <f t="shared" si="1"/>
-        <v>0.036</v>
-      </c>
-      <c r="J12" s="17"/>
-      <c r="K12" s="19"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="16"/>
-      <c r="C13" s="21" t="s">
-        <v>101</v>
-      </c>
-      <c r="D13" s="30">
-        <v>30.064</v>
-      </c>
-      <c r="E13" s="30">
-        <v>30.016</v>
-      </c>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="I13" s="31">
+        <v>-0.0580000000000034</v>
+      </c>
+      <c r="I16" s="17">
+        <f t="shared" si="2"/>
+        <v>-0.0920000000000023</v>
+      </c>
+      <c r="J16" s="17">
+        <v>0</v>
+      </c>
+      <c r="K16" s="22">
+        <f t="shared" si="3"/>
+        <v>0.0499999999999972</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="2:11">
+      <c r="B17" s="14"/>
+      <c r="C17" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="D17" s="16">
+        <v>30.156</v>
+      </c>
+      <c r="E17" s="16">
+        <v>30.078</v>
+      </c>
+      <c r="F17" s="16">
+        <v>30.218</v>
+      </c>
+      <c r="G17" s="16">
+        <v>30.202</v>
+      </c>
+      <c r="H17" s="17">
         <f t="shared" si="1"/>
-        <v>0.048</v>
-      </c>
-      <c r="J13" s="17"/>
-      <c r="K13" s="19"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="F14" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="G14" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="H14" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="I14" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="J14" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="K14" s="15" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="20"/>
-      <c r="C15" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="D15" s="30">
-        <v>30.15</v>
-      </c>
-      <c r="E15" s="30">
-        <v>30.172</v>
-      </c>
-      <c r="F15" s="30">
-        <v>30.094</v>
-      </c>
-      <c r="G15" s="30">
-        <v>30.012</v>
-      </c>
-      <c r="H15" s="31">
-        <f t="shared" ref="H15:H18" si="2">F15-D15</f>
-        <v>-0.056</v>
-      </c>
-      <c r="I15" s="31">
-        <f t="shared" ref="I15:I18" si="3">F15-E15</f>
-        <v>-0.078</v>
-      </c>
-      <c r="J15" s="31">
-        <v>0.0</v>
-      </c>
-      <c r="K15" s="34">
-        <f t="shared" ref="K15:K18" si="4">F15-G15</f>
-        <v>0.082</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="20"/>
-      <c r="C16" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="D16" s="30">
-        <v>30.138</v>
-      </c>
-      <c r="E16" s="30">
-        <v>30.172</v>
-      </c>
-      <c r="F16" s="30">
-        <v>30.08</v>
-      </c>
-      <c r="G16" s="30">
-        <v>30.03</v>
-      </c>
-      <c r="H16" s="31">
+        <v>0.0620000000000012</v>
+      </c>
+      <c r="I17" s="17">
         <f t="shared" si="2"/>
-        <v>-0.058</v>
-      </c>
-      <c r="I16" s="31">
+        <v>0.140000000000001</v>
+      </c>
+      <c r="J17" s="17">
+        <v>0</v>
+      </c>
+      <c r="K17" s="22">
         <f t="shared" si="3"/>
-        <v>-0.092</v>
-      </c>
-      <c r="J16" s="31">
-        <v>0.0</v>
-      </c>
-      <c r="K16" s="34">
-        <f t="shared" si="4"/>
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="20"/>
-      <c r="C17" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="D17" s="30">
-        <v>30.156</v>
-      </c>
-      <c r="E17" s="30">
-        <v>30.078</v>
-      </c>
-      <c r="F17" s="30">
-        <v>30.218</v>
-      </c>
-      <c r="G17" s="30">
-        <v>30.202</v>
-      </c>
-      <c r="H17" s="31">
+        <v>0.0159999999999982</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="2:11">
+      <c r="B18" s="23"/>
+      <c r="C18" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="D18" s="25">
+        <v>30.142</v>
+      </c>
+      <c r="E18" s="25">
+        <v>30.176</v>
+      </c>
+      <c r="F18" s="25">
+        <v>30.086</v>
+      </c>
+      <c r="G18" s="25">
+        <v>30.008</v>
+      </c>
+      <c r="H18" s="26">
+        <f t="shared" si="1"/>
+        <v>-0.0560000000000009</v>
+      </c>
+      <c r="I18" s="26">
         <f t="shared" si="2"/>
-        <v>0.062</v>
-      </c>
-      <c r="I17" s="31">
+        <v>-0.0899999999999999</v>
+      </c>
+      <c r="J18" s="26">
+        <v>0</v>
+      </c>
+      <c r="K18" s="27">
         <f t="shared" si="3"/>
-        <v>0.14</v>
-      </c>
-      <c r="J17" s="31">
-        <v>0.0</v>
-      </c>
-      <c r="K17" s="34">
-        <f t="shared" si="4"/>
-        <v>0.016</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="22"/>
-      <c r="C18" s="23" t="s">
-        <v>110</v>
-      </c>
-      <c r="D18" s="35">
-        <v>30.142</v>
-      </c>
-      <c r="E18" s="35">
-        <v>30.176</v>
-      </c>
-      <c r="F18" s="35">
-        <v>30.086</v>
-      </c>
-      <c r="G18" s="35">
-        <v>30.008</v>
-      </c>
-      <c r="H18" s="36">
-        <f t="shared" si="2"/>
-        <v>-0.056</v>
-      </c>
-      <c r="I18" s="36">
-        <f t="shared" si="3"/>
-        <v>-0.09</v>
-      </c>
-      <c r="J18" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="K18" s="37">
-        <f t="shared" si="4"/>
-        <v>0.078</v>
+        <v>0.0779999999999994</v>
       </c>
     </row>
   </sheetData>
@@ -2456,6 +3282,7 @@
     <mergeCell ref="B10:B13"/>
     <mergeCell ref="B14:B18"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>